--- a/artfynd/A 56004-2025 artfynd.xlsx
+++ b/artfynd/A 56004-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56004-2025 artfynd.xlsx
+++ b/artfynd/A 56004-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56004-2025 artfynd.xlsx
+++ b/artfynd/A 56004-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56004-2025 artfynd.xlsx
+++ b/artfynd/A 56004-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,122 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130016233</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sjökärret, Sjökärret, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>470420</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6539228</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Varningsläte.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56004-2025 artfynd.xlsx
+++ b/artfynd/A 56004-2025 artfynd.xlsx
@@ -817,9 +817,13 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sjökärret, Sjökärret, Vg</t>
@@ -876,7 +880,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Varningsläte.</t>
+          <t>Varningsläte från 2 talltitor med andra mesar.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 56004-2025 artfynd.xlsx
+++ b/artfynd/A 56004-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130016233</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56004-2025 artfynd.xlsx
+++ b/artfynd/A 56004-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130016233</v>
       </c>
       <c r="B3" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56004-2025 artfynd.xlsx
+++ b/artfynd/A 56004-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>56926</v>
+        <v>57016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56004-2025 artfynd.xlsx
+++ b/artfynd/A 56004-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56004-2025 artfynd.xlsx
+++ b/artfynd/A 56004-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56004-2025 artfynd.xlsx
+++ b/artfynd/A 56004-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56004-2025 artfynd.xlsx
+++ b/artfynd/A 56004-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56004-2025 artfynd.xlsx
+++ b/artfynd/A 56004-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>57073</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130016233</v>
       </c>
       <c r="B3" t="n">
-        <v>57985</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 56004-2025 artfynd.xlsx
+++ b/artfynd/A 56004-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129461402</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,8 +914,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130016233</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>